--- a/outputs/reports/sequence_window_sample_summary.xlsx
+++ b/outputs/reports/sequence_window_sample_summary.xlsx
@@ -465,7 +465,7 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
